--- a/DOC_runs/alkalinityAnalysis.xlsx
+++ b/DOC_runs/alkalinityAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11008"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phill\Dropbox\DOC_expts\DOC_runs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bob.hall/Dropbox/DOC_expts/doc_uptake/DOC_runs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51ABC1EE-0AA0-4E76-9E19-918D9A0084DD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07F11A2-50CA-E74C-8727-D3641FC8972A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="7200" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="55280" yWindow="6620" windowWidth="21960" windowHeight="18220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -180,9 +180,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,20 +462,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:K32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>2</v>
       </c>
@@ -505,7 +504,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -530,7 +529,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>7</v>
       </c>
@@ -561,7 +560,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -592,7 +591,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>9</v>
       </c>
@@ -623,7 +622,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>10</v>
       </c>
@@ -654,7 +653,7 @@
         <v>5.6799999999999988</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>11</v>
       </c>
@@ -685,7 +684,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>12</v>
       </c>
@@ -716,7 +715,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>13</v>
       </c>
@@ -747,7 +746,7 @@
         <v>5.2400000000000011</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>14</v>
       </c>
@@ -778,7 +777,7 @@
         <v>5.4399999999999977</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>15</v>
       </c>
@@ -809,7 +808,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -840,7 +839,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>17</v>
       </c>
@@ -871,7 +870,7 @@
         <v>5.2400000000000011</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>18</v>
       </c>
@@ -902,7 +901,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>19</v>
       </c>
@@ -933,7 +932,7 @@
         <v>5.2400000000000011</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>20</v>
       </c>
@@ -964,7 +963,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>21</v>
       </c>
@@ -995,376 +994,388 @@
         <v>5.0400000000000009</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="1" t="s">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19">
         <v>4.7</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19">
         <v>8.08</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19">
         <v>9.5</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19">
         <v>4.4800000000000004</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19">
         <f t="shared" si="0"/>
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J19" s="1">
+      <c r="H19">
+        <v>20</v>
+      </c>
+      <c r="I19">
+        <v>0.05</v>
+      </c>
+      <c r="J19">
         <f t="shared" si="1"/>
         <v>1.9199999999999997</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20">
         <v>9.5</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20">
         <v>8.1199999999999992</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20">
         <v>14.3</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20">
         <v>4.46</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20">
         <f t="shared" si="0"/>
         <v>4.8000000000000004E-3</v>
       </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J20" s="1">
+      <c r="H20">
+        <v>20</v>
+      </c>
+      <c r="I20">
+        <v>0.05</v>
+      </c>
+      <c r="J20">
         <f t="shared" si="1"/>
         <v>1.92</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="1" t="s">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21">
         <v>14.3</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21">
         <v>8.08</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21">
         <v>19</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21">
         <v>4.51</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21">
         <f t="shared" si="0"/>
         <v>4.6999999999999993E-3</v>
       </c>
-      <c r="H21" s="1">
-        <v>20</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J21" s="1">
+      <c r="H21">
+        <v>20</v>
+      </c>
+      <c r="I21">
+        <v>0.05</v>
+      </c>
+      <c r="J21">
         <f t="shared" si="1"/>
         <v>1.8799999999999997</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="1" t="s">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22">
         <v>19</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22">
         <v>8.1</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22">
         <v>23.7</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22">
         <v>4.5</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22">
         <f t="shared" si="0"/>
         <v>4.6999999999999993E-3</v>
       </c>
-      <c r="H22" s="1">
-        <v>20</v>
-      </c>
-      <c r="I22" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J22" s="1">
+      <c r="H22">
+        <v>20</v>
+      </c>
+      <c r="I22">
+        <v>0.05</v>
+      </c>
+      <c r="J22">
         <f t="shared" si="1"/>
         <v>1.8799999999999997</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23">
         <v>1.2</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23">
         <v>8.08</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23">
         <v>14.6</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23">
         <v>4.55</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23">
         <f t="shared" si="0"/>
         <v>1.34E-2</v>
       </c>
-      <c r="H23" s="1">
-        <v>20</v>
-      </c>
-      <c r="I23" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J23" s="1">
+      <c r="H23">
+        <v>20</v>
+      </c>
+      <c r="I23">
+        <v>0.05</v>
+      </c>
+      <c r="J23">
         <f t="shared" si="1"/>
         <v>5.36</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="1" t="s">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24">
         <v>14.6</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24">
         <v>8.14</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24">
         <v>28</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24">
         <v>4.54</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24">
         <f t="shared" si="0"/>
         <v>1.34E-2</v>
       </c>
-      <c r="H24" s="1">
-        <v>20</v>
-      </c>
-      <c r="I24" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J24" s="1">
+      <c r="H24">
+        <v>20</v>
+      </c>
+      <c r="I24">
+        <v>0.05</v>
+      </c>
+      <c r="J24">
         <f t="shared" si="1"/>
         <v>5.36</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="1" t="s">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25">
         <v>28</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25">
         <v>8.02</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25">
         <v>41.2</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25">
         <v>4.54</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25">
         <f t="shared" si="0"/>
         <v>1.3200000000000003E-2</v>
       </c>
-      <c r="H25" s="1">
-        <v>20</v>
-      </c>
-      <c r="I25" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J25" s="1">
+      <c r="H25">
+        <v>20</v>
+      </c>
+      <c r="I25">
+        <v>0.05</v>
+      </c>
+      <c r="J25">
         <f t="shared" si="1"/>
         <v>5.2800000000000011</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="1" t="s">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26">
         <v>1.5</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26">
         <v>8.08</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26">
         <v>14.2</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26">
         <v>4.5199999999999996</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26">
         <f t="shared" si="0"/>
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="H26" s="1">
-        <v>20</v>
-      </c>
-      <c r="I26" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J26" s="1">
+      <c r="H26">
+        <v>20</v>
+      </c>
+      <c r="I26">
+        <v>0.05</v>
+      </c>
+      <c r="J26">
         <f t="shared" si="1"/>
         <v>5.08</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="1" t="s">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27">
         <v>14.2</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27">
         <v>8.0399999999999991</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27">
         <v>27.7</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27">
         <v>4.5199999999999996</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27">
         <f t="shared" si="0"/>
         <v>1.35E-2</v>
       </c>
-      <c r="H27" s="1">
-        <v>20</v>
-      </c>
-      <c r="I27" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J27" s="1">
+      <c r="H27">
+        <v>20</v>
+      </c>
+      <c r="I27">
+        <v>0.05</v>
+      </c>
+      <c r="J27">
         <f t="shared" si="1"/>
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="1" t="s">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28">
         <v>27.7</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28">
         <v>8.01</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28">
         <v>40.9</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28">
         <v>4.54</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28">
         <f t="shared" si="0"/>
         <v>1.32E-2</v>
       </c>
-      <c r="H28" s="1">
-        <v>20</v>
-      </c>
-      <c r="I28" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J28" s="1">
+      <c r="H28">
+        <v>20</v>
+      </c>
+      <c r="I28">
+        <v>0.05</v>
+      </c>
+      <c r="J28">
         <f t="shared" si="1"/>
         <v>5.28</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="1" t="s">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29">
         <v>0.4</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29">
         <v>8.0399999999999991</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29">
         <v>13.5</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29">
         <v>4.53</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29">
         <f t="shared" si="0"/>
         <v>1.3099999999999999E-2</v>
       </c>
-      <c r="H29" s="1">
-        <v>20</v>
-      </c>
-      <c r="I29" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J29" s="1">
+      <c r="H29">
+        <v>20</v>
+      </c>
+      <c r="I29">
+        <v>0.05</v>
+      </c>
+      <c r="J29">
         <f t="shared" si="1"/>
         <v>5.2399999999999984</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="s">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30">
         <v>13.5</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30">
         <v>8.09</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30">
         <v>26.4</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30">
         <v>4.53</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30">
         <f t="shared" si="0"/>
         <v>1.2899999999999998E-2</v>
       </c>
-      <c r="H30" s="1">
-        <v>20</v>
-      </c>
-      <c r="I30" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="J30" s="1">
+      <c r="H30">
+        <v>20</v>
+      </c>
+      <c r="I30">
+        <v>0.05</v>
+      </c>
+      <c r="J30">
         <f t="shared" si="1"/>
         <v>5.1599999999999984</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K31">
+        <f>AVERAGE(J3:J18,J23:J30)</f>
+        <v>5.3049999999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K32">
+        <f>STDEV(J3:J18,J23:J30)</f>
+        <v>0.15096789177777517</v>
       </c>
     </row>
   </sheetData>
